--- a/Data/EC/NIT-9014801495.xlsx
+++ b/Data/EC/NIT-9014801495.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laura Wilches\Documents\2_ Macro Comfenalco Cartagena\Macro Aviso Incumplimiento y demás\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Operaciones\OneDrive - NIYARAKY COLOMBIA SAS OLD2\Escritorio\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F7DBF271-EE6A-4616-9E62-7A3DA51448B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6978B954-23FF-48B4-9DB2-4561AD02E66D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{07163E80-550B-41B9-8651-3CACC057BC93}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{7DCDCA4C-CD1A-4648-A79A-9D9A04FED9DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -686,22 +686,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>633769</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>55950</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>437794</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>125025</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D95A6CD9-1C94-A51E-027D-768BD8CC5850}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED957908-2194-FD6E-CE66-271922A2E1ED}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -710,7 +710,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -723,7 +723,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="890944" y="236925"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1052,23 +1052,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93A21A7A-DED5-4D48-8256-1DDFEA09BE1E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54B97741-2237-4FE6-8AFE-29D8210F8DC2}">
   <dimension ref="B2:J175"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.59765625" customWidth="1"/>
-    <col min="2" max="2" width="18.9296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.06640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.73046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="41.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
@@ -1081,7 +1081,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1092,7 +1092,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1103,7 +1103,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1114,8 +1114,8 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>84</v>
       </c>
@@ -1130,8 +1130,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1146,8 +1146,8 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>85</v>
       </c>
@@ -1162,8 +1162,8 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>86</v>
       </c>
@@ -1182,7 +1182,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1211,7 +1211,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1234,7 +1234,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1257,7 +1257,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1280,7 +1280,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1303,7 +1303,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1326,7 +1326,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1349,7 +1349,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1372,7 +1372,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1395,7 +1395,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1418,7 +1418,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1441,7 +1441,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1464,7 +1464,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1487,7 +1487,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1510,7 +1510,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1533,7 +1533,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1556,7 +1556,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1579,7 +1579,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1602,7 +1602,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1625,7 +1625,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1648,7 +1648,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1671,7 +1671,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1694,7 +1694,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1717,7 +1717,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1740,7 +1740,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1763,7 +1763,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1786,7 +1786,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1809,7 +1809,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1832,7 +1832,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1855,7 +1855,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1878,7 +1878,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -1901,7 +1901,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -1924,7 +1924,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -1947,7 +1947,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -1970,7 +1970,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -1993,7 +1993,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -2016,7 +2016,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -2039,7 +2039,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -2062,7 +2062,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -2085,7 +2085,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -2108,7 +2108,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -2131,7 +2131,7 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
@@ -2154,7 +2154,7 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
@@ -2177,7 +2177,7 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
@@ -2200,7 +2200,7 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
@@ -2223,7 +2223,7 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
@@ -2246,7 +2246,7 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
@@ -2269,7 +2269,7 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
@@ -2292,7 +2292,7 @@
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>8</v>
       </c>
@@ -2315,7 +2315,7 @@
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>8</v>
       </c>
@@ -2338,7 +2338,7 @@
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
         <v>8</v>
       </c>
@@ -2361,7 +2361,7 @@
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
         <v>8</v>
       </c>
@@ -2384,7 +2384,7 @@
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="15" t="s">
         <v>8</v>
       </c>
@@ -2407,7 +2407,7 @@
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
         <v>8</v>
       </c>
@@ -2430,7 +2430,7 @@
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
         <v>8</v>
       </c>
@@ -2453,7 +2453,7 @@
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="15" t="s">
         <v>8</v>
       </c>
@@ -2476,7 +2476,7 @@
       <c r="I70" s="19"/>
       <c r="J70" s="20"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="15" t="s">
         <v>8</v>
       </c>
@@ -2499,7 +2499,7 @@
       <c r="I71" s="19"/>
       <c r="J71" s="20"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="15" t="s">
         <v>8</v>
       </c>
@@ -2522,7 +2522,7 @@
       <c r="I72" s="19"/>
       <c r="J72" s="20"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="15" t="s">
         <v>8</v>
       </c>
@@ -2545,7 +2545,7 @@
       <c r="I73" s="19"/>
       <c r="J73" s="20"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="15" t="s">
         <v>8</v>
       </c>
@@ -2568,7 +2568,7 @@
       <c r="I74" s="19"/>
       <c r="J74" s="20"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="15" t="s">
         <v>8</v>
       </c>
@@ -2591,7 +2591,7 @@
       <c r="I75" s="19"/>
       <c r="J75" s="20"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="15" t="s">
         <v>8</v>
       </c>
@@ -2614,7 +2614,7 @@
       <c r="I76" s="19"/>
       <c r="J76" s="20"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="15" t="s">
         <v>8</v>
       </c>
@@ -2637,7 +2637,7 @@
       <c r="I77" s="19"/>
       <c r="J77" s="20"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="15" t="s">
         <v>8</v>
       </c>
@@ -2660,7 +2660,7 @@
       <c r="I78" s="19"/>
       <c r="J78" s="20"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="15" t="s">
         <v>8</v>
       </c>
@@ -2683,7 +2683,7 @@
       <c r="I79" s="19"/>
       <c r="J79" s="20"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="15" t="s">
         <v>8</v>
       </c>
@@ -2706,7 +2706,7 @@
       <c r="I80" s="19"/>
       <c r="J80" s="20"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="15" t="s">
         <v>8</v>
       </c>
@@ -2729,7 +2729,7 @@
       <c r="I81" s="19"/>
       <c r="J81" s="20"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="15" t="s">
         <v>8</v>
       </c>
@@ -2752,7 +2752,7 @@
       <c r="I82" s="19"/>
       <c r="J82" s="20"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="15" t="s">
         <v>8</v>
       </c>
@@ -2775,7 +2775,7 @@
       <c r="I83" s="19"/>
       <c r="J83" s="20"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="15" t="s">
         <v>8</v>
       </c>
@@ -2798,7 +2798,7 @@
       <c r="I84" s="19"/>
       <c r="J84" s="20"/>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="15" t="s">
         <v>45</v>
       </c>
@@ -2821,7 +2821,7 @@
       <c r="I85" s="19"/>
       <c r="J85" s="20"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="15" t="s">
         <v>45</v>
       </c>
@@ -2844,7 +2844,7 @@
       <c r="I86" s="19"/>
       <c r="J86" s="20"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="15" t="s">
         <v>45</v>
       </c>
@@ -2867,7 +2867,7 @@
       <c r="I87" s="19"/>
       <c r="J87" s="20"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="15" t="s">
         <v>45</v>
       </c>
@@ -2890,7 +2890,7 @@
       <c r="I88" s="19"/>
       <c r="J88" s="20"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="15" t="s">
         <v>45</v>
       </c>
@@ -2913,7 +2913,7 @@
       <c r="I89" s="19"/>
       <c r="J89" s="20"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="15" t="s">
         <v>8</v>
       </c>
@@ -2936,7 +2936,7 @@
       <c r="I90" s="19"/>
       <c r="J90" s="20"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" s="15" t="s">
         <v>8</v>
       </c>
@@ -2959,7 +2959,7 @@
       <c r="I91" s="19"/>
       <c r="J91" s="20"/>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="15" t="s">
         <v>8</v>
       </c>
@@ -2982,7 +2982,7 @@
       <c r="I92" s="19"/>
       <c r="J92" s="20"/>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="15" t="s">
         <v>8</v>
       </c>
@@ -3005,7 +3005,7 @@
       <c r="I93" s="19"/>
       <c r="J93" s="20"/>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="15" t="s">
         <v>8</v>
       </c>
@@ -3028,7 +3028,7 @@
       <c r="I94" s="19"/>
       <c r="J94" s="20"/>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="15" t="s">
         <v>8</v>
       </c>
@@ -3051,7 +3051,7 @@
       <c r="I95" s="19"/>
       <c r="J95" s="20"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="15" t="s">
         <v>8</v>
       </c>
@@ -3074,7 +3074,7 @@
       <c r="I96" s="19"/>
       <c r="J96" s="20"/>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B97" s="15" t="s">
         <v>8</v>
       </c>
@@ -3097,7 +3097,7 @@
       <c r="I97" s="19"/>
       <c r="J97" s="20"/>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B98" s="15" t="s">
         <v>8</v>
       </c>
@@ -3120,7 +3120,7 @@
       <c r="I98" s="19"/>
       <c r="J98" s="20"/>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B99" s="15" t="s">
         <v>8</v>
       </c>
@@ -3143,7 +3143,7 @@
       <c r="I99" s="19"/>
       <c r="J99" s="20"/>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B100" s="15" t="s">
         <v>8</v>
       </c>
@@ -3166,7 +3166,7 @@
       <c r="I100" s="19"/>
       <c r="J100" s="20"/>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B101" s="15" t="s">
         <v>8</v>
       </c>
@@ -3189,7 +3189,7 @@
       <c r="I101" s="19"/>
       <c r="J101" s="20"/>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B102" s="15" t="s">
         <v>8</v>
       </c>
@@ -3212,7 +3212,7 @@
       <c r="I102" s="19"/>
       <c r="J102" s="20"/>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B103" s="15" t="s">
         <v>8</v>
       </c>
@@ -3235,7 +3235,7 @@
       <c r="I103" s="19"/>
       <c r="J103" s="20"/>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B104" s="15" t="s">
         <v>8</v>
       </c>
@@ -3258,7 +3258,7 @@
       <c r="I104" s="19"/>
       <c r="J104" s="20"/>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B105" s="15" t="s">
         <v>8</v>
       </c>
@@ -3281,7 +3281,7 @@
       <c r="I105" s="19"/>
       <c r="J105" s="20"/>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B106" s="15" t="s">
         <v>8</v>
       </c>
@@ -3304,7 +3304,7 @@
       <c r="I106" s="19"/>
       <c r="J106" s="20"/>
     </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="107" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B107" s="15" t="s">
         <v>8</v>
       </c>
@@ -3327,7 +3327,7 @@
       <c r="I107" s="19"/>
       <c r="J107" s="20"/>
     </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="108" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B108" s="15" t="s">
         <v>8</v>
       </c>
@@ -3350,7 +3350,7 @@
       <c r="I108" s="19"/>
       <c r="J108" s="20"/>
     </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="109" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B109" s="15" t="s">
         <v>8</v>
       </c>
@@ -3373,7 +3373,7 @@
       <c r="I109" s="19"/>
       <c r="J109" s="20"/>
     </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="110" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B110" s="15" t="s">
         <v>8</v>
       </c>
@@ -3396,7 +3396,7 @@
       <c r="I110" s="19"/>
       <c r="J110" s="20"/>
     </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="111" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B111" s="15" t="s">
         <v>8</v>
       </c>
@@ -3419,7 +3419,7 @@
       <c r="I111" s="19"/>
       <c r="J111" s="20"/>
     </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="112" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B112" s="15" t="s">
         <v>8</v>
       </c>
@@ -3442,7 +3442,7 @@
       <c r="I112" s="19"/>
       <c r="J112" s="20"/>
     </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="113" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B113" s="15" t="s">
         <v>8</v>
       </c>
@@ -3465,7 +3465,7 @@
       <c r="I113" s="19"/>
       <c r="J113" s="20"/>
     </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="114" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B114" s="15" t="s">
         <v>8</v>
       </c>
@@ -3488,7 +3488,7 @@
       <c r="I114" s="19"/>
       <c r="J114" s="20"/>
     </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="115" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B115" s="15" t="s">
         <v>8</v>
       </c>
@@ -3511,7 +3511,7 @@
       <c r="I115" s="19"/>
       <c r="J115" s="20"/>
     </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="116" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B116" s="15" t="s">
         <v>8</v>
       </c>
@@ -3534,7 +3534,7 @@
       <c r="I116" s="19"/>
       <c r="J116" s="20"/>
     </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="117" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B117" s="15" t="s">
         <v>8</v>
       </c>
@@ -3557,7 +3557,7 @@
       <c r="I117" s="19"/>
       <c r="J117" s="20"/>
     </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="118" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B118" s="15" t="s">
         <v>8</v>
       </c>
@@ -3580,7 +3580,7 @@
       <c r="I118" s="19"/>
       <c r="J118" s="20"/>
     </row>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="119" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B119" s="15" t="s">
         <v>8</v>
       </c>
@@ -3603,7 +3603,7 @@
       <c r="I119" s="19"/>
       <c r="J119" s="20"/>
     </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="120" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B120" s="15" t="s">
         <v>8</v>
       </c>
@@ -3626,7 +3626,7 @@
       <c r="I120" s="19"/>
       <c r="J120" s="20"/>
     </row>
-    <row r="121" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="121" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B121" s="15" t="s">
         <v>8</v>
       </c>
@@ -3649,7 +3649,7 @@
       <c r="I121" s="19"/>
       <c r="J121" s="20"/>
     </row>
-    <row r="122" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="122" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B122" s="15" t="s">
         <v>8</v>
       </c>
@@ -3672,7 +3672,7 @@
       <c r="I122" s="19"/>
       <c r="J122" s="20"/>
     </row>
-    <row r="123" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="123" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B123" s="15" t="s">
         <v>8</v>
       </c>
@@ -3695,7 +3695,7 @@
       <c r="I123" s="19"/>
       <c r="J123" s="20"/>
     </row>
-    <row r="124" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="124" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B124" s="15" t="s">
         <v>8</v>
       </c>
@@ -3718,7 +3718,7 @@
       <c r="I124" s="19"/>
       <c r="J124" s="20"/>
     </row>
-    <row r="125" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="125" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B125" s="15" t="s">
         <v>8</v>
       </c>
@@ -3741,7 +3741,7 @@
       <c r="I125" s="19"/>
       <c r="J125" s="20"/>
     </row>
-    <row r="126" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="126" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B126" s="15" t="s">
         <v>8</v>
       </c>
@@ -3764,7 +3764,7 @@
       <c r="I126" s="19"/>
       <c r="J126" s="20"/>
     </row>
-    <row r="127" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="127" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B127" s="15" t="s">
         <v>8</v>
       </c>
@@ -3787,7 +3787,7 @@
       <c r="I127" s="19"/>
       <c r="J127" s="20"/>
     </row>
-    <row r="128" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="128" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B128" s="15" t="s">
         <v>8</v>
       </c>
@@ -3810,7 +3810,7 @@
       <c r="I128" s="19"/>
       <c r="J128" s="20"/>
     </row>
-    <row r="129" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="129" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B129" s="15" t="s">
         <v>8</v>
       </c>
@@ -3833,7 +3833,7 @@
       <c r="I129" s="19"/>
       <c r="J129" s="20"/>
     </row>
-    <row r="130" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="130" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B130" s="15" t="s">
         <v>8</v>
       </c>
@@ -3856,7 +3856,7 @@
       <c r="I130" s="19"/>
       <c r="J130" s="20"/>
     </row>
-    <row r="131" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="131" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B131" s="15" t="s">
         <v>8</v>
       </c>
@@ -3879,7 +3879,7 @@
       <c r="I131" s="19"/>
       <c r="J131" s="20"/>
     </row>
-    <row r="132" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="132" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B132" s="15" t="s">
         <v>8</v>
       </c>
@@ -3902,7 +3902,7 @@
       <c r="I132" s="19"/>
       <c r="J132" s="20"/>
     </row>
-    <row r="133" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="133" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B133" s="15" t="s">
         <v>8</v>
       </c>
@@ -3925,7 +3925,7 @@
       <c r="I133" s="19"/>
       <c r="J133" s="20"/>
     </row>
-    <row r="134" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="134" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B134" s="15" t="s">
         <v>8</v>
       </c>
@@ -3948,7 +3948,7 @@
       <c r="I134" s="19"/>
       <c r="J134" s="20"/>
     </row>
-    <row r="135" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="135" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B135" s="15" t="s">
         <v>45</v>
       </c>
@@ -3971,7 +3971,7 @@
       <c r="I135" s="19"/>
       <c r="J135" s="20"/>
     </row>
-    <row r="136" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="136" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B136" s="15" t="s">
         <v>45</v>
       </c>
@@ -3994,7 +3994,7 @@
       <c r="I136" s="19"/>
       <c r="J136" s="20"/>
     </row>
-    <row r="137" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="137" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B137" s="15" t="s">
         <v>45</v>
       </c>
@@ -4017,7 +4017,7 @@
       <c r="I137" s="19"/>
       <c r="J137" s="20"/>
     </row>
-    <row r="138" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="138" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B138" s="15" t="s">
         <v>45</v>
       </c>
@@ -4040,7 +4040,7 @@
       <c r="I138" s="19"/>
       <c r="J138" s="20"/>
     </row>
-    <row r="139" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="139" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B139" s="15" t="s">
         <v>8</v>
       </c>
@@ -4063,7 +4063,7 @@
       <c r="I139" s="19"/>
       <c r="J139" s="20"/>
     </row>
-    <row r="140" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="140" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B140" s="15" t="s">
         <v>8</v>
       </c>
@@ -4086,7 +4086,7 @@
       <c r="I140" s="19"/>
       <c r="J140" s="20"/>
     </row>
-    <row r="141" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="141" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B141" s="15" t="s">
         <v>8</v>
       </c>
@@ -4109,7 +4109,7 @@
       <c r="I141" s="19"/>
       <c r="J141" s="20"/>
     </row>
-    <row r="142" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="142" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B142" s="15" t="s">
         <v>8</v>
       </c>
@@ -4132,7 +4132,7 @@
       <c r="I142" s="19"/>
       <c r="J142" s="20"/>
     </row>
-    <row r="143" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="143" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B143" s="15" t="s">
         <v>8</v>
       </c>
@@ -4155,7 +4155,7 @@
       <c r="I143" s="19"/>
       <c r="J143" s="20"/>
     </row>
-    <row r="144" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="144" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B144" s="15" t="s">
         <v>8</v>
       </c>
@@ -4178,7 +4178,7 @@
       <c r="I144" s="19"/>
       <c r="J144" s="20"/>
     </row>
-    <row r="145" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="145" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B145" s="15" t="s">
         <v>8</v>
       </c>
@@ -4201,7 +4201,7 @@
       <c r="I145" s="19"/>
       <c r="J145" s="20"/>
     </row>
-    <row r="146" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="146" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B146" s="15" t="s">
         <v>8</v>
       </c>
@@ -4224,7 +4224,7 @@
       <c r="I146" s="19"/>
       <c r="J146" s="20"/>
     </row>
-    <row r="147" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="147" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B147" s="15" t="s">
         <v>8</v>
       </c>
@@ -4247,7 +4247,7 @@
       <c r="I147" s="19"/>
       <c r="J147" s="20"/>
     </row>
-    <row r="148" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="148" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B148" s="15" t="s">
         <v>8</v>
       </c>
@@ -4270,7 +4270,7 @@
       <c r="I148" s="19"/>
       <c r="J148" s="20"/>
     </row>
-    <row r="149" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="149" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B149" s="15" t="s">
         <v>8</v>
       </c>
@@ -4293,7 +4293,7 @@
       <c r="I149" s="19"/>
       <c r="J149" s="20"/>
     </row>
-    <row r="150" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="150" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B150" s="15" t="s">
         <v>8</v>
       </c>
@@ -4316,7 +4316,7 @@
       <c r="I150" s="19"/>
       <c r="J150" s="20"/>
     </row>
-    <row r="151" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="151" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B151" s="15" t="s">
         <v>8</v>
       </c>
@@ -4339,7 +4339,7 @@
       <c r="I151" s="19"/>
       <c r="J151" s="20"/>
     </row>
-    <row r="152" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="152" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B152" s="15" t="s">
         <v>8</v>
       </c>
@@ -4362,7 +4362,7 @@
       <c r="I152" s="19"/>
       <c r="J152" s="20"/>
     </row>
-    <row r="153" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="153" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B153" s="15" t="s">
         <v>8</v>
       </c>
@@ -4385,7 +4385,7 @@
       <c r="I153" s="19"/>
       <c r="J153" s="20"/>
     </row>
-    <row r="154" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="154" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B154" s="15" t="s">
         <v>8</v>
       </c>
@@ -4408,7 +4408,7 @@
       <c r="I154" s="19"/>
       <c r="J154" s="20"/>
     </row>
-    <row r="155" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="155" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B155" s="15" t="s">
         <v>8</v>
       </c>
@@ -4431,7 +4431,7 @@
       <c r="I155" s="19"/>
       <c r="J155" s="20"/>
     </row>
-    <row r="156" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="156" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B156" s="15" t="s">
         <v>8</v>
       </c>
@@ -4454,7 +4454,7 @@
       <c r="I156" s="19"/>
       <c r="J156" s="20"/>
     </row>
-    <row r="157" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="157" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B157" s="15" t="s">
         <v>8</v>
       </c>
@@ -4477,7 +4477,7 @@
       <c r="I157" s="19"/>
       <c r="J157" s="20"/>
     </row>
-    <row r="158" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="158" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B158" s="15" t="s">
         <v>8</v>
       </c>
@@ -4500,7 +4500,7 @@
       <c r="I158" s="19"/>
       <c r="J158" s="20"/>
     </row>
-    <row r="159" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="159" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B159" s="15" t="s">
         <v>8</v>
       </c>
@@ -4523,7 +4523,7 @@
       <c r="I159" s="19"/>
       <c r="J159" s="20"/>
     </row>
-    <row r="160" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="160" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B160" s="15" t="s">
         <v>8</v>
       </c>
@@ -4546,7 +4546,7 @@
       <c r="I160" s="19"/>
       <c r="J160" s="20"/>
     </row>
-    <row r="161" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="161" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B161" s="15" t="s">
         <v>8</v>
       </c>
@@ -4569,7 +4569,7 @@
       <c r="I161" s="19"/>
       <c r="J161" s="20"/>
     </row>
-    <row r="162" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="162" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B162" s="15" t="s">
         <v>8</v>
       </c>
@@ -4592,7 +4592,7 @@
       <c r="I162" s="19"/>
       <c r="J162" s="20"/>
     </row>
-    <row r="163" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="163" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B163" s="15" t="s">
         <v>8</v>
       </c>
@@ -4615,7 +4615,7 @@
       <c r="I163" s="19"/>
       <c r="J163" s="20"/>
     </row>
-    <row r="164" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="164" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B164" s="15" t="s">
         <v>8</v>
       </c>
@@ -4638,7 +4638,7 @@
       <c r="I164" s="19"/>
       <c r="J164" s="20"/>
     </row>
-    <row r="165" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="165" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B165" s="15" t="s">
         <v>8</v>
       </c>
@@ -4661,7 +4661,7 @@
       <c r="I165" s="19"/>
       <c r="J165" s="20"/>
     </row>
-    <row r="166" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="166" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B166" s="15" t="s">
         <v>8</v>
       </c>
@@ -4684,7 +4684,7 @@
       <c r="I166" s="19"/>
       <c r="J166" s="20"/>
     </row>
-    <row r="167" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="167" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B167" s="15" t="s">
         <v>8</v>
       </c>
@@ -4707,7 +4707,7 @@
       <c r="I167" s="19"/>
       <c r="J167" s="20"/>
     </row>
-    <row r="168" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="168" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B168" s="15" t="s">
         <v>8</v>
       </c>
@@ -4730,7 +4730,7 @@
       <c r="I168" s="19"/>
       <c r="J168" s="20"/>
     </row>
-    <row r="169" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="169" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B169" s="21" t="s">
         <v>8</v>
       </c>
@@ -4753,7 +4753,7 @@
       <c r="I169" s="25"/>
       <c r="J169" s="26"/>
     </row>
-    <row r="174" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="174" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B174" s="32" t="s">
         <v>92</v>
       </c>
@@ -4764,7 +4764,7 @@
       <c r="I174" s="1"/>
       <c r="J174" s="1"/>
     </row>
-    <row r="175" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="175" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B175" s="32" t="s">
         <v>91</v>
       </c>
